--- a/Result/profitability/1436.xlsx
+++ b/Result/profitability/1436.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.47</v>
+        <v>0.97</v>
       </c>
       <c r="N2" t="n">
-        <v>53.4275</v>
+        <v>54.62375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.90125</v>
+        <v>0.6937500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>54.345</v>
+        <v>54.53</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.08</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.60875</v>
       </c>
       <c r="N4" t="n">
-        <v>54.265</v>
+        <v>53.81375000000001</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.05</v>
       </c>
       <c r="M5" t="n">
-        <v>0.54625</v>
+        <v>0.33125</v>
       </c>
       <c r="N5" t="n">
-        <v>53.55500000000001</v>
+        <v>54.98</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>-0.05</v>
       </c>
       <c r="M6" t="n">
-        <v>0.26875</v>
+        <v>-0.08125</v>
       </c>
       <c r="N6" t="n">
-        <v>54.77125</v>
+        <v>56.415</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1152,10 +1152,10 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.02</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.14</v>
+        <v>-0.02625</v>
       </c>
       <c r="N7" t="n">
-        <v>56.29625</v>
+        <v>57.3375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1276,16 +1276,16 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.08</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.07250000000000001</v>
+        <v>0.0225</v>
       </c>
       <c r="N8" t="n">
-        <v>57.88124999999999</v>
+        <v>59.375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1412,7 +1412,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1436</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>410</v>
+      </c>
+      <c r="D75" t="n">
+        <v>159</v>
+      </c>
+      <c r="E75" t="n">
+        <v>251</v>
+      </c>
+      <c r="F75" t="n">
+        <v>61.17</v>
+      </c>
+      <c r="G75" t="n">
+        <v>167</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>40.71%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-49</v>
+      </c>
+      <c r="J75" t="n">
+        <v>118</v>
+      </c>
+      <c r="K75" t="n">
+        <v>87</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.5325</v>
+      </c>
+      <c r="N75" t="n">
+        <v>54.63625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-2.451612903225806</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2427874847622917</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.7926267281105991</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2290536467751658</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
